--- a/employment_forms/048_workforce_pipeline_intake_form--employment_forms.xlsx
+++ b/employment_forms/048_workforce_pipeline_intake_form--employment_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,13 +437,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E16"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="8" customWidth="1" min="2" max="2"/>
-    <col width="17" customWidth="1" min="3" max="3"/>
-    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="27" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -525,10 +525,14 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>first_name</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
+          <t>First Name</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Enter your first name</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
           <t>no</t>
@@ -548,10 +552,14 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>last_name</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
+          <t>Last Name</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Enter your last name</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
           <t>no</t>
@@ -571,10 +579,14 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>contact_email</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
+          <t>Contact Email</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Enter your contact email address</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
           <t>no</t>
@@ -594,10 +606,14 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>contact_phone</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
+          <t>Contact Phone</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Enter your contact phone number</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
           <t>no</t>
@@ -612,15 +628,19 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>page_1</t>
+          <t>page_5</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>job_title</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
+          <t>Job Title</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Select your job title - Software Engineer, Data Scientist, Project Manager, or Other</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
           <t>no</t>
@@ -635,15 +655,19 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>page_2</t>
+          <t>page_6</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>job_type</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
+          <t>Job Type</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Select multiple job types - Full-time, Contract, Internship, or Part-time</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
           <t>no</t>
@@ -658,15 +682,19 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>page_2</t>
+          <t>page_7</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>resume</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
+          <t>Resume</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Upload or paste your resume</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
           <t>no</t>
@@ -681,15 +709,19 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>page_3</t>
+          <t>page_8</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>availability</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
+          <t>Availability (Start Date)</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Enter your start date availability</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
           <t>no</t>
@@ -699,20 +731,24 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>page_1</t>
+          <t>page_9</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>availability</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
+          <t>Availability (End Date)</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Enter your end date availability</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
           <t>no</t>
@@ -727,15 +763,19 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>page_3</t>
+          <t>page_10</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>availability</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
+          <t>Work Hours</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Enter your work hours</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
           <t>no</t>
@@ -750,15 +790,19 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>page_3</t>
+          <t>page_11</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>resume</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
+          <t>Job Description</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Describe your job experience and skills</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
           <t>no</t>
@@ -768,44 +812,25 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>time</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>page_3</t>
+          <t>page_12</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>job_description</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
+          <t>Page 12</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Enter your work hours</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>page_1</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>resume</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -850,7 +875,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>page_1_choices</t>
+          <t>page_5_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -867,7 +892,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>page_1_choices</t>
+          <t>page_5_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -884,7 +909,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>page_1_choices</t>
+          <t>page_5_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -901,7 +926,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>page_1_choices</t>
+          <t>page_5_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -918,7 +943,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>page_2_choices</t>
+          <t>page_6_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -935,7 +960,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>page_2_choices</t>
+          <t>page_6_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -952,7 +977,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>page_2_choices</t>
+          <t>page_6_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -969,7 +994,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>page_2_choices</t>
+          <t>page_6_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
